--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487895_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487895_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LAFUENTE VELAZQUEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.6908</v>
+        <v>5.1287</v>
       </c>
       <c r="E2" t="n">
-        <v>1.8506</v>
+        <v>2.7158</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8402</v>
+        <v>2.4129</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9412</v>
+        <v>4.0312</v>
       </c>
       <c r="H2" t="n">
-        <v>4.0811</v>
+        <v>2.2474</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8601</v>
+        <v>1.7839</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3167</v>
+        <v>2.5374</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1425</v>
+        <v>1.5454</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1742</v>
+        <v>0.9919</v>
       </c>
       <c r="M2" t="n">
-        <v>1.6245</v>
+        <v>1.4939</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9387</v>
+        <v>0.7019</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6858</v>
+        <v>0.792</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.7055</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2866</v>
+        <v>0.2837</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.1753</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7589</v>
+        <v>0.1084</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8314</v>
+        <v>0.8137</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.8314</v>
+        <v>1.0437</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>J. LAFUENTE VELAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9063</v>
+        <v>5.0529</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7577</v>
+        <v>1.5944</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1487</v>
+        <v>3.4585</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0312</v>
+        <v>7.9412</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2474</v>
+        <v>4.0811</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7839</v>
+        <v>3.8601</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5374</v>
+        <v>6.3167</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5454</v>
+        <v>3.1425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9919</v>
+        <v>3.1742</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4939</v>
+        <v>1.6245</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7019</v>
+        <v>0.9387</v>
       </c>
       <c r="O3" t="n">
-        <v>0.792</v>
+        <v>0.6858</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-2.7055</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0406</v>
+        <v>-4.1624</v>
       </c>
       <c r="R3" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0614</v>
+        <v>0.6487000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2172</v>
+        <v>0.2715</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1558</v>
+        <v>0.3772</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8137</v>
+        <v>-0.8314</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0437</v>
+        <v>-0.8314</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7928</v>
+        <v>4.5007</v>
       </c>
       <c r="E4" t="n">
-        <v>6.9272</v>
+        <v>6.6057</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.1344</v>
+        <v>-2.105</v>
       </c>
       <c r="G4" t="n">
         <v>1.9195</v>
@@ -766,13 +766,13 @@
         <v>1.0406</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5382</v>
+        <v>0.2461</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7235</v>
+        <v>0.402</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1852</v>
+        <v>-0.1559</v>
       </c>
       <c r="V4" t="n">
         <v>2.3351</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9268</v>
+        <v>3.9414</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9437</v>
+        <v>2.405</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9831</v>
+        <v>1.5363</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0858</v>
+        <v>3.7012</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2752</v>
+        <v>2.1255</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1894</v>
+        <v>1.5757</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6492</v>
+        <v>2.3012</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6672</v>
+        <v>1.5174</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.018</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4366</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
         <v>0.6081</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1714</v>
+        <v>0.792</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4162</v>
+        <v>1.0406</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6649</v>
+        <v>1.0406</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6298</v>
+        <v>0.4732</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7482</v>
+        <v>0.1039</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8815</v>
+        <v>0.3694</v>
       </c>
       <c r="V5" t="n">
-        <v>1.6275</v>
+        <v>-1.2737</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6275</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2737</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.6633</v>
+        <v>3.3564</v>
       </c>
       <c r="E6" t="n">
-        <v>1.804</v>
+        <v>0.9018</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8593</v>
+        <v>2.4546</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7012</v>
+        <v>1.0858</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1255</v>
+        <v>1.2752</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5757</v>
+        <v>-0.1894</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3012</v>
+        <v>0.6492</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5174</v>
+        <v>0.6672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7838000000000001</v>
+        <v>-0.018</v>
       </c>
       <c r="M6" t="n">
-        <v>1.4</v>
+        <v>0.4366</v>
       </c>
       <c r="N6" t="n">
         <v>0.6081</v>
       </c>
       <c r="O6" t="n">
-        <v>0.792</v>
+        <v>-0.1714</v>
       </c>
       <c r="P6" t="n">
-        <v>1.0406</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0406</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1951</v>
+        <v>1.0594</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4972</v>
+        <v>0.7063</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6923</v>
+        <v>0.3531</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2737</v>
+        <v>1.6275</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6275</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3855</v>
+        <v>2.5991</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.8837</v>
       </c>
       <c r="F7" t="n">
-        <v>3.013</v>
+        <v>3.4828</v>
       </c>
       <c r="G7" t="n">
         <v>4.6474</v>
@@ -1000,13 +1000,13 @@
         <v>1.0406</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1807</v>
+        <v>0.0328</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3477</v>
+        <v>0.0915</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5284</v>
+        <v>-0.0586</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1807</v>
+        <v>2.4743</v>
       </c>
       <c r="E8" t="n">
         <v>1.8669</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3138</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="G8" t="n">
         <v>0.6281</v>
@@ -1078,13 +1078,13 @@
         <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8449</v>
+        <v>-0.5513</v>
       </c>
       <c r="T8" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.225</v>
       </c>
       <c r="V8" t="n">
         <v>1.9813</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HERNANDEZ RODRIGUEZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4094</v>
+        <v>0.1802</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7604</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.351</v>
+        <v>0.1706</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4094</v>
+        <v>-0.6701</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0192</v>
+        <v>-1.0872</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4286</v>
+        <v>0.4172</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6952</v>
+        <v>-0.029</v>
       </c>
       <c r="K9" t="n">
         <v>0.0192</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7144</v>
+        <v>-0.0482</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2857</v>
+        <v>-0.6411</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-1.1064</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2857</v>
+        <v>0.4654</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.1904</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.0386</v>
       </c>
       <c r="U9" t="n">
-        <v>0.06519999999999999</v>
+        <v>-0.229</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>M. HERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5611</v>
+        <v>-0.4094</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5262</v>
+        <v>-0.7604</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.035</v>
+        <v>0.351</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6701</v>
+        <v>-0.4094</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0872</v>
+        <v>0.0192</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4172</v>
+        <v>-0.4286</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.029</v>
+        <v>-0.6952</v>
       </c>
       <c r="K10" t="n">
         <v>0.0192</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0482</v>
+        <v>-0.7144</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6411</v>
+        <v>0.2857</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1064</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4654</v>
+        <v>0.2857</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9317</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4972</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4345</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8395</v>
+        <v>-3.5324</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.0263</v>
+        <v>-2.455</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8132</v>
+        <v>-1.0774</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5578</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>0.762</v>
+        <v>0.0692</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4658</v>
+        <v>0.0372</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2962</v>
+        <v>0.032</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6275</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5083</v>
+        <v>-4.7376</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6358</v>
+        <v>-5.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1275</v>
+        <v>0.3624</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3757</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1326</v>
+        <v>-0.3619</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5748</v>
+        <v>-0.039</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5578</v>
+        <v>-0.3229</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>18.2279</v>
+        <v>18.5543</v>
       </c>
       <c r="E13" t="n">
-        <v>6.573900000000002</v>
+        <v>6.9001</v>
       </c>
       <c r="F13" t="n">
-        <v>11.654</v>
+        <v>11.6541</v>
       </c>
       <c r="G13" t="n">
         <v>16.9414</v>
@@ -1447,13 +1447,13 @@
         <v>6.1053</v>
       </c>
       <c r="L13" t="n">
-        <v>5.143300000000001</v>
+        <v>5.143299999999999</v>
       </c>
       <c r="M13" t="n">
         <v>5.692800000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.5935999999999997</v>
+        <v>-0.5935999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>6.286700000000001</v>
@@ -1468,13 +1468,13 @@
         <v>10.4059</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3832</v>
+        <v>1.7095</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0695</v>
+        <v>1.3959</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3138000000000001</v>
+        <v>0.3139</v>
       </c>
       <c r="V13" t="n">
         <v>3.025</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.49</v>
+        <v>2.0191</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5937</v>
+        <v>1.0935</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8963</v>
+        <v>0.9257</v>
       </c>
       <c r="G14" t="n">
         <v>0.2655</v>
@@ -1546,13 +1546,13 @@
         <v>1.0406</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0322</v>
+        <v>0.5614</v>
       </c>
       <c r="T14" t="n">
-        <v>2.0746</v>
+        <v>0.5744</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0424</v>
+        <v>-0.013</v>
       </c>
       <c r="V14" t="n">
         <v>1.1923</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1093</v>
+        <v>1.5482</v>
       </c>
       <c r="E15" t="n">
-        <v>1.313</v>
+        <v>1.6345</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2037</v>
+        <v>-0.0862</v>
       </c>
       <c r="G15" t="n">
         <v>1.0187</v>
@@ -1624,13 +1624,13 @@
         <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3503</v>
+        <v>0.0886</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3262</v>
+        <v>-0.0047</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0241</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>0.0248</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1539</v>
+        <v>0.3619</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1277</v>
+        <v>0.0206</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0262</v>
+        <v>0.3413</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2573</v>
@@ -1702,13 +1702,13 @@
         <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.3052</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3849</v>
+        <v>0.2777</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2877</v>
+        <v>0.0275</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1428</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2765</v>
+        <v>-0.2281</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2247</v>
+        <v>-0.1176</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0518</v>
+        <v>-0.1106</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1474</v>
@@ -1780,13 +1780,13 @@
         <v>0.2081</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3373</v>
+        <v>-0.2888</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1957</v>
+        <v>-0.0886</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1416</v>
+        <v>-0.2003</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. OLAIZOLA GARIN</t>
+          <t>I. AIZPITARTE ARANZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7514</v>
+        <v>-0.235</v>
       </c>
       <c r="E18" t="n">
-        <v>1.44</v>
+        <v>-1.3003</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.1913</v>
+        <v>1.0653</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1043</v>
+        <v>0.0395</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8274</v>
+        <v>-0.2536</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2769</v>
+        <v>0.2931</v>
       </c>
       <c r="J18" t="n">
-        <v>2.8596</v>
+        <v>0.7050999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9786</v>
+        <v>0.3794</v>
       </c>
       <c r="L18" t="n">
-        <v>1.881</v>
+        <v>0.3257</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7553</v>
+        <v>-0.6656</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1512</v>
+        <v>-0.6329</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6041</v>
+        <v>-0.0326</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R18" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3373</v>
+        <v>0.5769</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3791</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0418</v>
+        <v>0.5011</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3103</v>
+        <v>-0.4352</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.3103</v>
+        <v>-0.4352</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. AIZPITARTE ARANZA</t>
+          <t>M. OLAIZOLA GARIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0272</v>
+        <v>-0.3815</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8361</v>
+        <v>1.8686</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8089</v>
+        <v>-2.2501</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0395</v>
+        <v>2.1043</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2536</v>
+        <v>0.8274</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2931</v>
+        <v>1.2769</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7050999999999999</v>
+        <v>2.8596</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3794</v>
+        <v>0.9786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3257</v>
+        <v>1.881</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6656</v>
+        <v>-0.7553</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6329</v>
+        <v>-0.1512</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0326</v>
+        <v>-0.6041</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2153</v>
+        <v>0.0326</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.46</v>
+        <v>0.0496</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2447</v>
+        <v>-0.0169</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4352</v>
+        <v>-2.3103</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.4352</v>
+        <v>-2.3103</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1081</v>
+        <v>-0.4398</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1037</v>
+        <v>0.7467</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2119</v>
+        <v>-1.1864</v>
       </c>
       <c r="G20" t="n">
         <v>-0.7224</v>
@@ -2014,13 +2014,13 @@
         <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8207</v>
+        <v>-0.1524</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0315</v>
+        <v>-0.3886</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2108</v>
+        <v>0.2362</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8137</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3813</v>
+        <v>-1.5662</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4304</v>
+        <v>-1.0733</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9509</v>
+        <v>-0.4929</v>
       </c>
       <c r="G21" t="n">
         <v>-0.1341</v>
@@ -2092,13 +2092,13 @@
         <v>1.6649</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4573</v>
+        <v>0.2723</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7202</v>
+        <v>0.0772</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2629</v>
+        <v>0.1951</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2477</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.0299</v>
+        <v>-3.206</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0583</v>
+        <v>-3.4869</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0284</v>
+        <v>0.2809</v>
       </c>
       <c r="G22" t="n">
         <v>-5.229</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>0.426</v>
+        <v>0.2498</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3163</v>
+        <v>-0.1123</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1097</v>
+        <v>0.3621</v>
       </c>
       <c r="V22" t="n">
         <v>1.9813</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.919</v>
+        <v>-5.188</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4422</v>
+        <v>-4.2279</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4768</v>
+        <v>-0.9601</v>
       </c>
       <c r="G23" t="n">
         <v>-5.7474</v>
@@ -2248,13 +2248,13 @@
         <v>2.2893</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9604</v>
+        <v>-0.2294</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4509</v>
+        <v>-0.2366</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5095</v>
+        <v>0.0072</v>
       </c>
       <c r="V23" t="n">
         <v>-0.4599</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.4877</v>
+        <v>-8.769399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.2405</v>
+        <v>-6.8119</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2472</v>
+        <v>-1.9576</v>
       </c>
       <c r="G24" t="n">
         <v>-8.1318</v>
@@ -2326,13 +2326,13 @@
         <v>0.8325</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3747</v>
+        <v>-0.6564</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9663</v>
+        <v>-0.5376</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4084</v>
+        <v>-0.1187</v>
       </c>
       <c r="V24" t="n">
         <v>-0.8137</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.2279</v>
+        <v>-16.0848</v>
       </c>
       <c r="E25" t="n">
-        <v>-11.6541</v>
+        <v>-11.654</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.573799999999999</v>
+        <v>-4.430700000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-16.9414</v>
@@ -2404,13 +2404,13 @@
         <v>13.5276</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3833</v>
+        <v>0.7597999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-0.3137</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0696</v>
+        <v>1.0736</v>
       </c>
       <c r="V25" t="n">
         <v>-3.0249</v>
